--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1555,55 +1555,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67965646</v>
+        <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>93196</v>
+        <v>99270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1435</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norra Gussjön, kalkbrottet, Dlr</t>
+          <t>Gänsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508957</v>
+        <v>487867</v>
       </c>
       <c r="R9" t="n">
-        <v>6677153</v>
+        <v>6678802</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1625,17 +1615,17 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Ludvika</t>
+          <t>Grangärde</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,59 +1634,37 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>kalkmarkskog mellan kalkbrott</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>på varphög # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67965646</t>
+          <t>https://artportalen.se/Sighting/136953616</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67965657</v>
+        <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>87412</v>
+        <v>99270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,40 +1672,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3624</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norra Gussjön, kalkbrottet, Dlr</t>
+          <t>Gänsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509051</v>
+        <v>487916</v>
       </c>
       <c r="R10" t="n">
-        <v>6677258</v>
+        <v>6678732</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1759,17 +1721,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Ludvika</t>
+          <t>Grangärde</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,86 +1740,64 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>kalkmarkskog mellan kalkbrott</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>på varphög # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67965657</t>
+          <t>https://artportalen.se/Sighting/136953617</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128891264</v>
+        <v>67965646</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>93196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4189</v>
+        <v>1435</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1866,17 +1806,16 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norra Gussjöns gruvområde, Dlr</t>
+          <t>Norra Gussjön, kalkbrottet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509042</v>
+        <v>508957</v>
       </c>
       <c r="R11" t="n">
-        <v>6677249</v>
+        <v>6677153</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1903,12 +1842,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1923,12 +1862,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkmark.</t>
+          <t>kalkmarkskog mellan kalkbrott</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>på varphög # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1945,40 +1899,36 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128891264</t>
+          <t>https://artportalen.se/Sighting/67965646</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128891300</v>
+        <v>67965657</v>
       </c>
       <c r="B12" t="n">
-        <v>93215</v>
+        <v>87412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4368</v>
+        <v>3624</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>10</t>
@@ -1990,17 +1940,16 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norra Gussjöns gruvområde, Dlr</t>
+          <t>Norra Gussjön, kalkbrottet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508965</v>
+        <v>509051</v>
       </c>
       <c r="R12" t="n">
-        <v>6677173</v>
+        <v>6677258</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2027,12 +1976,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2047,12 +1996,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkmark.</t>
+          <t>kalkmarkskog mellan kalkbrott</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>på varphög # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2069,43 +2033,43 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128891300</t>
+          <t>https://artportalen.se/Sighting/67965657</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128891294</v>
+        <v>128891264</v>
       </c>
       <c r="B13" t="n">
-        <v>90636</v>
+        <v>91330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4900</v>
+        <v>4189</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barrmusseron</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucopaxillus cerealis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lasch) Singer</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2121,10 +2085,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509057</v>
+        <v>509042</v>
       </c>
       <c r="R13" t="n">
-        <v>6677260</v>
+        <v>6677249</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2193,54 +2157,65 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128891294</t>
+          <t>https://artportalen.se/Sighting/128891264</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2703670</v>
+        <v>128891300</v>
       </c>
       <c r="B14" t="n">
-        <v>98186</v>
+        <v>93215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220250</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sörvik, Dlr</t>
+          <t>Norra Gussjöns gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509108</v>
+        <v>508965</v>
       </c>
       <c r="R14" t="n">
-        <v>6677197</v>
+        <v>6677173</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2264,12 +2239,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2278,12 +2253,18 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>alkärr</t>
+          <t>Kalkmark.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2294,64 +2275,71 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Wieck</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Rapport hotade växter i Ludvika kommun</t>
-        </is>
-      </c>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2703670</t>
+          <t>https://artportalen.se/Sighting/128891300</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>62427610</v>
+        <v>128891294</v>
       </c>
       <c r="B15" t="n">
-        <v>98186</v>
+        <v>90636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220250</v>
+        <v>4900</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Barrmusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Leucopaxillus cerealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Lasch) Singer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sörvik, Dlr</t>
+          <t>Norra Gussjöns gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509157</v>
+        <v>509057</v>
       </c>
       <c r="R15" t="n">
-        <v>6677247</v>
+        <v>6677260</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2375,17 +2363,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Dalafloran [542]</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2394,92 +2377,82 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>alkärr</t>
+          <t>Kalkmark.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Inge Palmqvist</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Wieck</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Dalaflorans databas</t>
-        </is>
-      </c>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62427610</t>
+          <t>https://artportalen.se/Sighting/128891294</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128891238</v>
+        <v>2703670</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>98186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>220250</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norra Gussjöns gruvområde, Dlr</t>
+          <t>Sörvik, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508993</v>
+        <v>509108</v>
       </c>
       <c r="R16" t="n">
-        <v>6677205</v>
+        <v>6677197</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2503,12 +2476,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2517,18 +2490,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkmark.</t>
+          <t>alkärr</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2539,22 +2506,26 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Håkan Wieck</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Rapport hotade växter i Ludvika kommun</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128891238</t>
+          <t>https://artportalen.se/Sighting/2703670</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67965660</v>
+        <v>62427610</v>
       </c>
       <c r="B17" t="n">
-        <v>97977</v>
+        <v>98186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2562,36 +2533,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221944</v>
+        <v>220250</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norra Gussjön, kalkbrottet, Dlr</t>
+          <t>Sörvik, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509051</v>
+        <v>509157</v>
       </c>
       <c r="R17" t="n">
-        <v>6677258</v>
+        <v>6677247</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2615,12 +2587,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2004-12-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Dalafloran [542]</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2632,98 +2609,89 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>kalkmarkskog mellan kalkbrott</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>på varphög # Picea abies</t>
+          <t>alkärr</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Inge Palmqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Håkan Wieck</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Dalaflorans databas</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67965660</t>
+          <t>https://artportalen.se/Sighting/62427610</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4970626</v>
+        <v>128891238</v>
       </c>
       <c r="B18" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norra Gussjön, Dlr</t>
+          <t>Norra Gussjöns gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509025</v>
+        <v>508993</v>
       </c>
       <c r="R18" t="n">
-        <v>6677228</v>
+        <v>6677205</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2747,12 +2715,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2013-05-12</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2013-05-12</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2761,12 +2729,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>kalkbarrskog vid gruvhål</t>
+          <t>Kalkmark.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2783,16 +2757,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4970626</t>
+          <t>https://artportalen.se/Sighting/128891238</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6950895</v>
+        <v>67965660</v>
       </c>
       <c r="B19" t="n">
-        <v>101326</v>
+        <v>97977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2800,34 +2774,33 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norra Gussjön, Dlr</t>
+          <t>Norra Gussjön, kalkbrottet, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509052</v>
+        <v>509051</v>
       </c>
       <c r="R19" t="n">
-        <v>6677275</v>
+        <v>6677258</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2854,12 +2827,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2013-09-17</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2013-09-17</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2871,9 +2844,29 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>kalkbarrskog vid gruvhål</t>
+          <t>kalkmarkskog mellan kalkbrott</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>på varphög # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2890,57 +2883,59 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6950895</t>
+          <t>https://artportalen.se/Sighting/67965660</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128891242</v>
+        <v>4970626</v>
       </c>
       <c r="B20" t="n">
-        <v>87323</v>
+        <v>101326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>249228</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norra Gussjöns gruvområde, Dlr</t>
+          <t>Norra Gussjön, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508993</v>
+        <v>509025</v>
       </c>
       <c r="R20" t="n">
-        <v>6677205</v>
+        <v>6677228</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2964,12 +2959,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2013-05-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2013-05-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2978,18 +2973,12 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkmark.</t>
+          <t>kalkbarrskog vid gruvhål</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3006,62 +2995,51 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128891242</t>
+          <t>https://artportalen.se/Sighting/4970626</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128891229</v>
+        <v>6950895</v>
       </c>
       <c r="B21" t="n">
-        <v>87297</v>
+        <v>101326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6003296</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norra Gussjöns gruvområde, Dlr</t>
+          <t>Norra Gussjön, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508966</v>
+        <v>509052</v>
       </c>
       <c r="R21" t="n">
-        <v>6677127</v>
+        <v>6677275</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3088,17 +3066,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2013-09-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Kött + brun.</t>
+          <t>2013-09-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3107,18 +3080,12 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkmark.</t>
+          <t>kalkbarrskog vid gruvhål</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3135,51 +3102,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128891229</t>
+          <t>https://artportalen.se/Sighting/6950895</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>66596200</v>
+        <v>128891242</v>
       </c>
       <c r="B22" t="n">
-        <v>96458</v>
+        <v>87323</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2818</v>
+        <v>249228</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gettjärnsberget, Dlr</t>
+          <t>Norra Gussjöns gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490111</v>
+        <v>508993</v>
       </c>
       <c r="R22" t="n">
-        <v>6666070</v>
+        <v>6677205</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3201,22 +3171,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Grangärde</t>
+          <t>Ludvika</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2017-07-05</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2017-07-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>sydbrant</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3225,22 +3190,269 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkmark.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristoffer Hylander</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristoffer Hylander</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128891242</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128891229</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87297</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norra Gussjöns gruvområde, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>508966</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6677127</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kött + brun.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkmark.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128891229</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>66596200</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gettjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>490111</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6666070</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2017-07-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2017-07-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sydbrant</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/66596200</t>
         </is>
@@ -3269,6 +3481,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 4522-2023 artfynd.xlsx
+++ b/artfynd/S 4522-2023 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>136953616</v>
       </c>
       <c r="B9" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136953617</v>
       </c>
       <c r="B10" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
